--- a/Data/Home/BedroomTwo.HumanState.xlsx
+++ b/Data/Home/BedroomTwo.HumanState.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H227"/>
+  <dimension ref="A1:I253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709251493</v>
+        <v>1711844108</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709251992</v>
+        <v>1711844861</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709252286</v>
+        <v>1711845291</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709262175</v>
+        <v>1711874022</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +605,7 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709266274</v>
+        <v>1711877622</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +638,11 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +661,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709280537</v>
+        <v>1711877867</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +675,7 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +694,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709283953</v>
+        <v>1711877880</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +708,11 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +731,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709285789</v>
+        <v>1711879353</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -725,6 +745,7 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +764,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709245247</v>
+        <v>1711928969</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +778,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +797,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709245801</v>
+        <v>1711929577</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +811,7 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +830,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709246080</v>
+        <v>1711930035</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +844,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +863,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709266716</v>
+        <v>1711959628</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +877,7 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +896,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709268869</v>
+        <v>1711962372</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -885,6 +910,11 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +933,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709270218</v>
+        <v>1711964506</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -917,6 +947,7 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +966,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709331001</v>
+        <v>1712018114</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +980,11 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +1003,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709331560</v>
+        <v>1712018748</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -981,6 +1017,7 @@
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1036,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709331890</v>
+        <v>1712019102</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1013,6 +1050,7 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1069,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709349513</v>
+        <v>1712051426</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1045,6 +1083,7 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1102,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709351473</v>
+        <v>1712052534</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1077,6 +1116,11 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1139,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709357228</v>
+        <v>1712053007</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1109,6 +1153,7 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1172,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709417693</v>
+        <v>1712055498</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1141,6 +1186,11 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1209,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709418200</v>
+        <v>1712055553</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1173,6 +1223,7 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1242,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709418503</v>
+        <v>1712058370</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1256,11 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1279,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709448736</v>
+        <v>1712060355</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1237,6 +1293,7 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1312,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709449696</v>
+        <v>1712102723</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1326,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1345,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709450000</v>
+        <v>1712103350</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1301,6 +1359,7 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1378,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709450922</v>
+        <v>1712103743</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1333,6 +1392,7 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1411,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709451120</v>
+        <v>1712138299</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1425,7 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1444,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709451144</v>
+        <v>1712141660</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1397,6 +1458,11 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1481,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709451747</v>
+        <v>1712143538</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1429,6 +1495,7 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1514,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709454172</v>
+        <v>1712189070</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1461,6 +1528,7 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1547,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709455966</v>
+        <v>1712189747</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1493,6 +1561,7 @@
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1580,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709503357</v>
+        <v>1712190118</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1525,6 +1594,7 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1613,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709503914</v>
+        <v>1712216205</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1557,6 +1627,7 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1646,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709504149</v>
+        <v>1712217443</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1589,6 +1660,11 @@
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1683,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709515577</v>
+        <v>1712217616</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1621,6 +1697,7 @@
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1716,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709519784</v>
+        <v>1712220616</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1730,11 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1753,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709527005</v>
+        <v>1712222670</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1685,6 +1767,7 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1786,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709529692</v>
+        <v>1712276994</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1717,6 +1800,7 @@
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1819,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709531465</v>
+        <v>1712277757</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1749,6 +1833,7 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1852,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709590096</v>
+        <v>1712278108</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1866,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1885,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709590715</v>
+        <v>1712289358</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1813,6 +1899,7 @@
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1918,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709590974</v>
+        <v>1712294367</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1845,6 +1932,11 @@
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1955,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709612733</v>
+        <v>1712306232</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1877,6 +1969,7 @@
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1988,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709615647</v>
+        <v>1712307516</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1909,6 +2002,11 @@
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +2025,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709622362</v>
+        <v>1712308020</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1941,6 +2039,7 @@
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2058,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709682092</v>
+        <v>1712310017</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1973,6 +2072,11 @@
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2095,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709682602</v>
+        <v>1712310215</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2005,6 +2109,7 @@
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2128,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709683452</v>
+        <v>1712310228</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2142,11 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2165,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709685207</v>
+        <v>1712316645</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,6 +2179,7 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2198,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709685702</v>
+        <v>1712367095</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2101,6 +2212,11 @@
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2235,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709711011</v>
+        <v>1712367798</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2133,6 +2249,7 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2268,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709768315</v>
+        <v>1712368634</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2282,11 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2305,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709768769</v>
+        <v>1712370921</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2319,7 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2338,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709769419</v>
+        <v>1712371543</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2229,6 +2352,11 @@
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2375,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709770691</v>
+        <v>1712401953</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2389,7 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2408,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709771276</v>
+        <v>1712403681</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2293,6 +2422,11 @@
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2445,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1709795879</v>
+        <v>1712404122</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2325,6 +2459,7 @@
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2478,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1709797498</v>
+        <v>1712405339</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2492,11 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2515,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1709797861</v>
+        <v>1712405567</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2389,6 +2529,7 @@
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2548,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1709799763</v>
+        <v>1712454119</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2421,6 +2562,11 @@
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2585,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1709800170</v>
+        <v>1712454720</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2453,6 +2599,7 @@
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2618,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1709802157</v>
+        <v>1712455591</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2485,6 +2632,11 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2655,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1709802411</v>
+        <v>1712456644</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2517,6 +2669,7 @@
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2688,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1709804233</v>
+        <v>1712457394</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2549,6 +2702,11 @@
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2725,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1709804647</v>
+        <v>1712485656</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2581,6 +2739,7 @@
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2758,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1709851575</v>
+        <v>1712495864</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2613,6 +2772,11 @@
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2795,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1709851996</v>
+        <v>1712496438</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2645,6 +2809,7 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2828,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1709852284</v>
+        <v>1712534555</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2677,6 +2842,7 @@
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2861,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1709860402</v>
+        <v>1712535166</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2709,6 +2875,7 @@
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2894,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1709863299</v>
+        <v>1712535543</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2741,6 +2908,7 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2927,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1709872579</v>
+        <v>1712552745</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2773,6 +2941,7 @@
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2960,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1709874735</v>
+        <v>1712556711</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2805,6 +2974,11 @@
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2997,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1709879897</v>
+        <v>1712568551</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2837,6 +3011,7 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +3030,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1709937397</v>
+        <v>1712572419</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2869,6 +3044,11 @@
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +3067,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1709937929</v>
+        <v>1712573444</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2901,6 +3081,7 @@
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3100,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1709938197</v>
+        <v>1712622987</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2933,6 +3114,7 @@
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3133,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1709962504</v>
+        <v>1712623648</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2965,6 +3147,7 @@
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3166,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1709964664</v>
+        <v>1712624014</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2997,6 +3180,7 @@
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3199,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1709966403</v>
+        <v>1712646211</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3029,6 +3213,7 @@
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3232,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1710023120</v>
+        <v>1712647485</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3061,6 +3246,11 @@
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3269,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1710023624</v>
+        <v>1712648000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3093,6 +3283,7 @@
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3302,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1710023955</v>
+        <v>1712650460</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3125,6 +3316,11 @@
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3339,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1710034893</v>
+        <v>1712650696</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3157,6 +3353,7 @@
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3372,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710038638</v>
+        <v>1712650711</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3189,6 +3386,11 @@
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3409,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710050850</v>
+        <v>1712654330</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3221,6 +3423,7 @@
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3442,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710053546</v>
+        <v>1712656965</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3253,6 +3456,11 @@
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3479,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710055166</v>
+        <v>1712658976</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3285,6 +3493,7 @@
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3512,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710108451</v>
+        <v>1712707073</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3317,6 +3526,7 @@
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3545,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710109003</v>
+        <v>1712707819</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3349,6 +3559,7 @@
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3578,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710109208</v>
+        <v>1712708175</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3381,6 +3592,7 @@
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3611,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710134981</v>
+        <v>1712720257</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3413,6 +3625,7 @@
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3644,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710138058</v>
+        <v>1712724429</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3445,6 +3658,11 @@
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3681,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710147710</v>
+        <v>1712737196</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3477,6 +3695,7 @@
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3714,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710197638</v>
+        <v>1712738482</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3509,6 +3728,11 @@
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3751,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710198226</v>
+        <v>1712738894</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3541,6 +3765,7 @@
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3784,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1710198543</v>
+        <v>1712741319</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3573,6 +3798,11 @@
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3821,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1710220149</v>
+        <v>1712741496</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3605,6 +3835,7 @@
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3854,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1710225575</v>
+        <v>1712744239</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3637,6 +3868,11 @@
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3891,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1710227439</v>
+        <v>1712746231</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3669,6 +3905,7 @@
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3924,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1710289865</v>
+        <v>1712792909</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3701,6 +3938,7 @@
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3957,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1710290418</v>
+        <v>1712793568</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3733,6 +3971,7 @@
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +3990,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1710291171</v>
+        <v>1712793901</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3765,6 +4004,7 @@
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +4023,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1710296745</v>
+        <v>1712805447</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3797,6 +4037,7 @@
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +4056,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1710297233</v>
+        <v>1712809560</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3829,6 +4070,11 @@
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +4093,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1710319285</v>
+        <v>1712820471</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3861,6 +4107,7 @@
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +4126,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1710320648</v>
+        <v>1712821541</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3893,6 +4140,11 @@
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4163,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1710320992</v>
+        <v>1712821897</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3925,6 +4177,7 @@
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4196,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1710322572</v>
+        <v>1712823836</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3957,6 +4210,11 @@
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4233,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1710322771</v>
+        <v>1712824029</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3989,6 +4247,7 @@
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4266,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1710324266</v>
+        <v>1712824045</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4021,6 +4280,11 @@
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4303,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1710324783</v>
+        <v>1712827785</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4053,6 +4317,7 @@
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4336,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1710374180</v>
+        <v>1712830464</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4085,6 +4350,11 @@
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4373,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1710374688</v>
+        <v>1712832339</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4117,6 +4387,7 @@
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4406,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1710375476</v>
+        <v>1712879027</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4149,6 +4420,7 @@
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4439,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1710377414</v>
+        <v>1712879696</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4181,6 +4453,7 @@
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4472,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1710378107</v>
+        <v>1712880128</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4213,6 +4486,7 @@
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4505,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1710404204</v>
+        <v>1712895091</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4245,6 +4519,7 @@
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4538,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1710408892</v>
+        <v>1712900417</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4277,6 +4552,11 @@
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4575,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1710409441</v>
+        <v>1712913003</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4309,6 +4589,7 @@
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4608,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1710456764</v>
+        <v>1712918434</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4341,6 +4622,11 @@
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4645,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1710457395</v>
+        <v>1712920511</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4373,6 +4659,7 @@
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4678,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1710457769</v>
+        <v>1712971537</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4405,6 +4692,11 @@
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4715,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1710484753</v>
+        <v>1712972236</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4437,6 +4729,7 @@
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4748,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1710486837</v>
+        <v>1712973223</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4469,6 +4762,11 @@
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4785,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1710488414</v>
+        <v>1712980624</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4501,6 +4799,7 @@
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4818,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1710541285</v>
+        <v>1712981448</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4533,6 +4832,11 @@
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4855,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1710541729</v>
+        <v>1713007608</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4565,6 +4869,7 @@
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4888,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1710542070</v>
+        <v>1713014480</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4597,6 +4902,11 @@
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4925,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1710551789</v>
+        <v>1713014693</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4629,6 +4939,7 @@
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +4958,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1710555038</v>
+        <v>1713058584</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4661,6 +4972,11 @@
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +4995,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1710563963</v>
+        <v>1713059283</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4693,6 +5009,7 @@
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4711,7 +5028,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1710566221</v>
+        <v>1713060210</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4725,6 +5042,11 @@
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4743,7 +5065,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1710573856</v>
+        <v>1713063968</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4757,6 +5079,7 @@
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4775,7 +5098,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1710627706</v>
+        <v>1713064627</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4789,6 +5112,11 @@
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4807,7 +5135,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1710628207</v>
+        <v>1713095005</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4821,6 +5149,7 @@
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4839,7 +5168,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1710628534</v>
+        <v>1713139044</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4853,6 +5182,7 @@
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4871,7 +5201,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1710658052</v>
+        <v>1713139707</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4885,6 +5215,7 @@
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4903,7 +5234,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1710662035</v>
+        <v>1713140144</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4917,6 +5248,7 @@
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4935,7 +5267,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1710662349</v>
+        <v>1713177437</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4949,6 +5281,7 @@
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4967,7 +5300,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1710714604</v>
+        <v>1713178583</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4981,6 +5314,11 @@
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4999,7 +5337,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1710715211</v>
+        <v>1713179026</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5013,6 +5351,7 @@
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5031,7 +5370,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1710715576</v>
+        <v>1713181223</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5045,6 +5384,11 @@
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5063,7 +5407,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1710737480</v>
+        <v>1713181430</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5077,6 +5421,7 @@
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5095,7 +5440,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1710740256</v>
+        <v>1713181449</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5109,6 +5454,11 @@
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5127,7 +5477,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1710740637</v>
+        <v>1713182308</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5141,6 +5491,7 @@
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5159,7 +5510,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1710800267</v>
+        <v>1713185501</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5173,6 +5524,11 @@
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5191,7 +5547,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1710800876</v>
+        <v>1713187604</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5205,6 +5561,7 @@
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5223,7 +5580,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1710801224</v>
+        <v>1713225464</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5237,6 +5594,7 @@
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5255,7 +5613,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1710827890</v>
+        <v>1713226185</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5269,6 +5627,7 @@
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5287,7 +5646,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1710830313</v>
+        <v>1713226511</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5301,6 +5660,7 @@
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5319,7 +5679,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1710831932</v>
+        <v>1713242517</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5333,6 +5693,7 @@
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5351,7 +5712,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1710889508</v>
+        <v>1713247536</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5365,6 +5726,11 @@
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5383,7 +5749,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1710890071</v>
+        <v>1713260509</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5397,6 +5763,7 @@
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5415,7 +5782,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1710890868</v>
+        <v>1713263814</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5429,6 +5796,11 @@
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5447,7 +5819,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1710895611</v>
+        <v>1713265944</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5461,6 +5833,7 @@
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5479,7 +5852,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1710896170</v>
+        <v>1713313404</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5493,6 +5866,7 @@
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5511,7 +5885,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1710917537</v>
+        <v>1713314087</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5525,6 +5899,7 @@
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5543,7 +5918,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1710922278</v>
+        <v>1713314520</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5557,6 +5932,7 @@
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5575,7 +5951,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1710922886</v>
+        <v>1713326367</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5589,6 +5965,7 @@
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5607,7 +5984,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1710978054</v>
+        <v>1713332486</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5621,6 +5998,11 @@
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5639,7 +6021,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1710978535</v>
+        <v>1713343201</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5653,6 +6035,7 @@
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5671,7 +6054,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1710979244</v>
+        <v>1713346673</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5685,6 +6068,11 @@
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5703,7 +6091,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1710982698</v>
+        <v>1713351495</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5717,6 +6105,7 @@
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5735,7 +6124,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1710983327</v>
+        <v>1713354295</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5749,6 +6138,11 @@
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5767,7 +6161,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1711005786</v>
+        <v>1713355738</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5781,6 +6175,7 @@
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5799,7 +6194,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1711060499</v>
+        <v>1713397869</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5813,6 +6208,7 @@
         </is>
       </c>
       <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5831,7 +6227,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1711061086</v>
+        <v>1713398578</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5845,6 +6241,7 @@
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5863,7 +6260,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1711061406</v>
+        <v>1713398969</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5877,6 +6274,7 @@
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5895,7 +6293,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1711071425</v>
+        <v>1713412339</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5909,6 +6307,7 @@
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5927,7 +6326,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1711075122</v>
+        <v>1713417241</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5941,6 +6340,11 @@
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5959,7 +6363,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1711086701</v>
+        <v>1713437426</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5973,6 +6377,7 @@
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5991,7 +6396,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1711088666</v>
+        <v>1713441404</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6005,6 +6410,11 @@
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6023,7 +6433,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1711089194</v>
+        <v>1713441807</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6037,6 +6447,7 @@
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6055,7 +6466,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1711091037</v>
+        <v>1713486700</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -6069,6 +6480,11 @@
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6087,7 +6503,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1711092509</v>
+        <v>1713487252</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -6101,6 +6517,7 @@
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6119,7 +6536,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1711146698</v>
+        <v>1713487663</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -6133,6 +6550,7 @@
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6151,7 +6569,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1711147301</v>
+        <v>1713518354</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6165,6 +6583,7 @@
         </is>
       </c>
       <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6183,7 +6602,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1711147648</v>
+        <v>1713520972</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6197,6 +6616,11 @@
         </is>
       </c>
       <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6215,7 +6639,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1711171747</v>
+        <v>1713522711</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6229,6 +6653,7 @@
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6247,7 +6672,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1711173690</v>
+        <v>1713576814</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -6261,6 +6686,11 @@
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6279,7 +6709,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1711175088</v>
+        <v>1713577515</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -6293,6 +6723,7 @@
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6311,7 +6742,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1711235769</v>
+        <v>1713578335</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -6325,6 +6756,11 @@
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6343,7 +6779,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1711236409</v>
+        <v>1713580336</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -6357,6 +6793,7 @@
         </is>
       </c>
       <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6375,7 +6812,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1711236714</v>
+        <v>1713580946</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -6389,6 +6826,11 @@
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6407,7 +6849,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1711246756</v>
+        <v>1713616845</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -6421,6 +6863,7 @@
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6439,7 +6882,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1711250896</v>
+        <v>1713663016</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6453,6 +6896,11 @@
         </is>
       </c>
       <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6471,7 +6919,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1711262112</v>
+        <v>1713663662</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6485,6 +6933,7 @@
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6503,7 +6952,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1711264100</v>
+        <v>1713664411</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6517,6 +6966,11 @@
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6535,7 +6989,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1711270043</v>
+        <v>1713665772</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6549,6 +7003,7 @@
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6567,7 +7022,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1711322228</v>
+        <v>1713666333</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6581,6 +7036,11 @@
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6599,7 +7059,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1711322719</v>
+        <v>1713696568</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6613,6 +7073,7 @@
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6631,7 +7092,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1711323011</v>
+        <v>1713742839</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -6645,6 +7106,7 @@
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6663,7 +7125,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1711333318</v>
+        <v>1713743554</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -6677,6 +7139,7 @@
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6695,7 +7158,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1711336644</v>
+        <v>1713743905</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -6709,6 +7172,7 @@
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6727,7 +7191,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1711351054</v>
+        <v>1713772166</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6741,6 +7205,7 @@
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6759,7 +7224,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1711353683</v>
+        <v>1713774855</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6773,6 +7238,11 @@
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6791,7 +7261,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1711357477</v>
+        <v>1713784397</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6805,6 +7275,7 @@
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6823,7 +7294,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1711360006</v>
+        <v>1713831676</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6837,6 +7308,11 @@
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6855,7 +7331,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1711362129</v>
+        <v>1713832390</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6869,6 +7345,7 @@
         </is>
       </c>
       <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6887,7 +7364,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1711411845</v>
+        <v>1713832809</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6901,6 +7378,7 @@
         </is>
       </c>
       <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6919,7 +7397,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1711412636</v>
+        <v>1713866075</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6933,6 +7411,7 @@
         </is>
       </c>
       <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -6951,7 +7430,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1711413010</v>
+        <v>1713869588</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6965,6 +7444,11 @@
         </is>
       </c>
       <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -6983,7 +7467,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1711451442</v>
+        <v>1713872165</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6997,6 +7481,7 @@
         </is>
       </c>
       <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7015,7 +7500,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1711454711</v>
+        <v>1713874906</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -7029,6 +7514,11 @@
         </is>
       </c>
       <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7047,7 +7537,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1711456428</v>
+        <v>1713876419</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -7061,6 +7551,7 @@
         </is>
       </c>
       <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7079,7 +7570,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>1711504233</v>
+        <v>1713916467</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -7093,6 +7584,7 @@
         </is>
       </c>
       <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7111,7 +7603,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1711505000</v>
+        <v>1713917109</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -7125,6 +7617,7 @@
         </is>
       </c>
       <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7143,7 +7636,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1711505947</v>
+        <v>1713917569</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -7157,6 +7650,7 @@
         </is>
       </c>
       <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7175,7 +7669,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1711510446</v>
+        <v>1713952492</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -7189,6 +7683,7 @@
         </is>
       </c>
       <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7207,7 +7702,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1711511069</v>
+        <v>1713953580</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -7221,6 +7716,11 @@
         </is>
       </c>
       <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7239,7 +7739,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1711541361</v>
+        <v>1713954005</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -7253,6 +7753,7 @@
         </is>
       </c>
       <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7271,7 +7772,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1711548065</v>
+        <v>1713956029</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -7285,6 +7786,11 @@
         </is>
       </c>
       <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7303,7 +7809,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>1711548824</v>
+        <v>1713956219</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -7317,6 +7823,7 @@
         </is>
       </c>
       <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7335,7 +7842,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>1711590619</v>
+        <v>1713956241</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -7349,6 +7856,11 @@
         </is>
       </c>
       <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7367,7 +7879,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1711591356</v>
+        <v>1713958944</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -7381,6 +7893,7 @@
         </is>
       </c>
       <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7399,7 +7912,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1711592460</v>
+        <v>1713962240</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -7413,6 +7926,11 @@
         </is>
       </c>
       <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7431,7 +7949,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>1711596599</v>
+        <v>1713964260</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -7445,6 +7963,7 @@
         </is>
       </c>
       <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7463,7 +7982,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1711597214</v>
+        <v>1714005287</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -7477,6 +7996,7 @@
         </is>
       </c>
       <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7495,7 +8015,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1711627130</v>
+        <v>1714005896</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -7509,6 +8029,7 @@
         </is>
       </c>
       <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -7527,7 +8048,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>1711628930</v>
+        <v>1714006251</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -7541,6 +8062,7 @@
         </is>
       </c>
       <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -7559,7 +8081,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1711629395</v>
+        <v>1714018267</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -7573,6 +8095,7 @@
         </is>
       </c>
       <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -7591,7 +8114,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1711631444</v>
+        <v>1714022377</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -7605,6 +8128,11 @@
         </is>
       </c>
       <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -7623,7 +8151,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1711631781</v>
+        <v>1714032091</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -7637,6 +8165,7 @@
         </is>
       </c>
       <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -7655,7 +8184,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1711634316</v>
+        <v>1714035326</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -7669,6 +8198,11 @@
         </is>
       </c>
       <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7687,7 +8221,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1711634991</v>
+        <v>1714042946</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -7701,6 +8235,909 @@
         </is>
       </c>
       <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>1714089422</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>BedroomTwo.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>1714090066</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>BedroomTwo.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>1714090492</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>BedroomTwo.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>1714104318</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>BedroomTwo.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>1714109429</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>BedroomTwo.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>1714124678</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>BedroomTwo.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>1714127360</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>BedroomTwo.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>1714129286</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>BedroomTwo.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>1714181349</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>BedroomTwo.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>1714182017</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>BedroomTwo.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>1714182935</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>BedroomTwo.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>1714188037</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>BedroomTwo.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>1714188661</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>BedroomTwo.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>1714219520</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>BedroomTwo.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>1714221217</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>BedroomTwo.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>1714221676</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>BedroomTwo.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>1714223670</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>BedroomTwo.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>1714223851</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>BedroomTwo.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>1714268979</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>BedroomTwo.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>1714269610</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>BedroomTwo.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>1714270449</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>BedroomTwo.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>1714271845</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>BedroomTwo.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>1714272558</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>BedroomTwo.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>1714304764</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>BedroomTwo.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>1714313035</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>BedroomTwo.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>1714313090</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>BedroomTwo.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
